--- a/payment_export/export_template/xlsx_report_register_icash.xlsx
+++ b/payment_export/export_template/xlsx_report_register_icash.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aommy\pabi_file\#4288\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aommy\pabi_file\000\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Register Number</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>Company Code</t>
+  </si>
+  <si>
+    <t>Partner Search key</t>
+  </si>
+  <si>
+    <t>Partner Name</t>
   </si>
 </sst>
 </file>
@@ -392,41 +398,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="38.25" customWidth="1"/>
-    <col min="3" max="3" width="20.25" customWidth="1"/>
-    <col min="4" max="4" width="37.25" customWidth="1"/>
+    <col min="2" max="2" width="19.375" customWidth="1"/>
+    <col min="3" max="3" width="37.5" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
+    <col min="6" max="6" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
